--- a/main/StructureDefinition-bc-sourceId-extension.xlsx
+++ b/main/StructureDefinition-bc-sourceId-extension.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-27T22:33:33+00:00</t>
+    <t>2026-03-25T22:00:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1287,7 +1287,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="5" hidden="true">
+    <row r="5">
       <c r="A5" t="s" s="2">
         <v>107</v>
       </c>
@@ -1703,7 +1703,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="9" hidden="true">
+    <row r="9">
       <c r="A9" t="s" s="2">
         <v>123</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>129</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
         <v>134</v>
       </c>
@@ -2535,12 +2535,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AK16">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
